--- a/data/trans_orig/IMC_inf_R-Dificultad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R-Dificultad-trans_orig.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -940,7 +940,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
